--- a/orchestrator/results/aime24_openai_scagent.xlsx
+++ b/orchestrator/results/aime24_openai_scagent.xlsx
@@ -413,13 +413,40 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="n">
         <v>0</v>
       </c>
+      <c r="C1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1" t="n">
+        <v>4</v>
+      </c>
+      <c r="G1" t="n">
+        <v>5</v>
+      </c>
+      <c r="H1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I1" t="n">
+        <v>7</v>
+      </c>
+      <c r="J1" t="n">
+        <v>8</v>
+      </c>
+      <c r="K1" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -430,6 +457,33 @@
       <c r="B2" t="n">
         <v>0</v>
       </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -440,6 +494,33 @@
       <c r="B3" t="n">
         <v>1</v>
       </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3" t="n">
+        <v>7</v>
+      </c>
+      <c r="I3" t="n">
+        <v>8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>9</v>
+      </c>
+      <c r="K3" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -450,6 +531,33 @@
       <c r="B4" t="n">
         <v>0</v>
       </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -462,6 +570,51 @@
           <t>all</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -472,6 +625,33 @@
       <c r="B6" t="b">
         <v>1</v>
       </c>
+      <c r="C6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -482,6 +662,33 @@
       <c r="B7" t="n">
         <v>0.6</v>
       </c>
+      <c r="C7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.63</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -492,6 +699,33 @@
       <c r="B8" t="n">
         <v>0</v>
       </c>
+      <c r="C8" t="n">
+        <v>48331</v>
+      </c>
+      <c r="D8" t="n">
+        <v>48331</v>
+      </c>
+      <c r="E8" t="n">
+        <v>48331</v>
+      </c>
+      <c r="F8" t="n">
+        <v>48331</v>
+      </c>
+      <c r="G8" t="n">
+        <v>48331</v>
+      </c>
+      <c r="H8" t="n">
+        <v>48331</v>
+      </c>
+      <c r="I8" t="n">
+        <v>48331</v>
+      </c>
+      <c r="J8" t="n">
+        <v>48331</v>
+      </c>
+      <c r="K8" t="n">
+        <v>48331</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -502,6 +736,33 @@
       <c r="B9" t="n">
         <v>0</v>
       </c>
+      <c r="C9" t="n">
+        <v>0.00241655</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.00241655</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.00241655</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.00241655</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.00241655</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.00241655</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.00241655</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.00241655</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.00241655</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -512,6 +773,33 @@
       <c r="B10" t="n">
         <v>0</v>
       </c>
+      <c r="C10" t="n">
+        <v>22418</v>
+      </c>
+      <c r="D10" t="n">
+        <v>22418</v>
+      </c>
+      <c r="E10" t="n">
+        <v>22418</v>
+      </c>
+      <c r="F10" t="n">
+        <v>22418</v>
+      </c>
+      <c r="G10" t="n">
+        <v>22418</v>
+      </c>
+      <c r="H10" t="n">
+        <v>22418</v>
+      </c>
+      <c r="I10" t="n">
+        <v>22418</v>
+      </c>
+      <c r="J10" t="n">
+        <v>22418</v>
+      </c>
+      <c r="K10" t="n">
+        <v>22418</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -522,6 +810,33 @@
       <c r="B11" t="n">
         <v>0</v>
       </c>
+      <c r="C11" t="n">
+        <v>0.008967200000000002</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.008967200000000002</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.008967200000000002</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.008967200000000002</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.008967200000000002</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.008967200000000002</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.008967200000000002</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.008967200000000002</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.008967200000000002</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -532,6 +847,33 @@
       <c r="B12" t="n">
         <v>48331</v>
       </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -542,6 +884,33 @@
       <c r="B13" t="n">
         <v>0.00241655</v>
       </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -550,7 +919,34 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>32107</v>
+        <v>22418</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -560,7 +956,34 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0128428</v>
+        <v>0.008967200000000002</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -572,6 +995,33 @@
       <c r="B16" t="n">
         <v>6972</v>
       </c>
+      <c r="C16" t="n">
+        <v>6972</v>
+      </c>
+      <c r="D16" t="n">
+        <v>13944</v>
+      </c>
+      <c r="E16" t="n">
+        <v>20916</v>
+      </c>
+      <c r="F16" t="n">
+        <v>27888</v>
+      </c>
+      <c r="G16" t="n">
+        <v>34860</v>
+      </c>
+      <c r="H16" t="n">
+        <v>41832</v>
+      </c>
+      <c r="I16" t="n">
+        <v>48804</v>
+      </c>
+      <c r="J16" t="n">
+        <v>55776</v>
+      </c>
+      <c r="K16" t="n">
+        <v>62748</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -582,6 +1032,33 @@
       <c r="B17" t="n">
         <v>0.0003486</v>
       </c>
+      <c r="C17" t="n">
+        <v>0.0003486</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.0006972</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.0010458</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.0013944</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.001743</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.0020916</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.0024402</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.0027888</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.0031374</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -592,6 +1069,33 @@
       <c r="B18" t="n">
         <v>324153</v>
       </c>
+      <c r="C18" t="n">
+        <v>324153</v>
+      </c>
+      <c r="D18" t="n">
+        <v>592627</v>
+      </c>
+      <c r="E18" t="n">
+        <v>870342</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1138843</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1432848</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1697261</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1947732</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2196875</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2505784</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -602,6 +1106,33 @@
       <c r="B19" t="n">
         <v>0.1296612</v>
       </c>
+      <c r="C19" t="n">
+        <v>0.1296612</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.2370508</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.3481368</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.4555372</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.5731392000000001</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.6789044000000001</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.7790928</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.87875</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.0023136</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -612,6 +1143,33 @@
       <c r="B20" t="n">
         <v>0</v>
       </c>
+      <c r="C20" t="n">
+        <v>6972</v>
+      </c>
+      <c r="D20" t="n">
+        <v>6972</v>
+      </c>
+      <c r="E20" t="n">
+        <v>6972</v>
+      </c>
+      <c r="F20" t="n">
+        <v>6972</v>
+      </c>
+      <c r="G20" t="n">
+        <v>6972</v>
+      </c>
+      <c r="H20" t="n">
+        <v>6972</v>
+      </c>
+      <c r="I20" t="n">
+        <v>6972</v>
+      </c>
+      <c r="J20" t="n">
+        <v>6972</v>
+      </c>
+      <c r="K20" t="n">
+        <v>6972</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -622,6 +1180,33 @@
       <c r="B21" t="n">
         <v>0</v>
       </c>
+      <c r="C21" t="n">
+        <v>0.0003486</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.0003486</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.0003486</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.0003486</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.0003486</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.0003486</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.0003486</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.0003486</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.0003486</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -632,6 +1217,33 @@
       <c r="B22" t="n">
         <v>0</v>
       </c>
+      <c r="C22" t="n">
+        <v>268474</v>
+      </c>
+      <c r="D22" t="n">
+        <v>277715</v>
+      </c>
+      <c r="E22" t="n">
+        <v>268501</v>
+      </c>
+      <c r="F22" t="n">
+        <v>294005</v>
+      </c>
+      <c r="G22" t="n">
+        <v>264413</v>
+      </c>
+      <c r="H22" t="n">
+        <v>250471</v>
+      </c>
+      <c r="I22" t="n">
+        <v>249143</v>
+      </c>
+      <c r="J22" t="n">
+        <v>308909</v>
+      </c>
+      <c r="K22" t="n">
+        <v>308696</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -642,6 +1254,33 @@
       <c r="B23" t="n">
         <v>0</v>
       </c>
+      <c r="C23" t="n">
+        <v>0.1073896</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.111086</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.1074004</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.117602</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.1057652</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1001884</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.09965720000000002</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.1235636</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.1234784</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -652,6 +1291,33 @@
       <c r="B24" t="n">
         <v>0</v>
       </c>
+      <c r="C24" t="n">
+        <v>30</v>
+      </c>
+      <c r="D24" t="n">
+        <v>30</v>
+      </c>
+      <c r="E24" t="n">
+        <v>30</v>
+      </c>
+      <c r="F24" t="n">
+        <v>30</v>
+      </c>
+      <c r="G24" t="n">
+        <v>30</v>
+      </c>
+      <c r="H24" t="n">
+        <v>30</v>
+      </c>
+      <c r="I24" t="n">
+        <v>30</v>
+      </c>
+      <c r="J24" t="n">
+        <v>30</v>
+      </c>
+      <c r="K24" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -662,6 +1328,33 @@
       <c r="B25" t="n">
         <v>30</v>
       </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -672,6 +1365,33 @@
       <c r="B26" t="n">
         <v>30</v>
       </c>
+      <c r="C26" t="n">
+        <v>30</v>
+      </c>
+      <c r="D26" t="n">
+        <v>60</v>
+      </c>
+      <c r="E26" t="n">
+        <v>90</v>
+      </c>
+      <c r="F26" t="n">
+        <v>120</v>
+      </c>
+      <c r="G26" t="n">
+        <v>150</v>
+      </c>
+      <c r="H26" t="n">
+        <v>180</v>
+      </c>
+      <c r="I26" t="n">
+        <v>210</v>
+      </c>
+      <c r="J26" t="n">
+        <v>240</v>
+      </c>
+      <c r="K26" t="n">
+        <v>270</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -682,6 +1402,33 @@
       <c r="B27" t="n">
         <v>0</v>
       </c>
+      <c r="C27" t="n">
+        <v>30</v>
+      </c>
+      <c r="D27" t="n">
+        <v>30</v>
+      </c>
+      <c r="E27" t="n">
+        <v>30</v>
+      </c>
+      <c r="F27" t="n">
+        <v>30</v>
+      </c>
+      <c r="G27" t="n">
+        <v>30</v>
+      </c>
+      <c r="H27" t="n">
+        <v>30</v>
+      </c>
+      <c r="I27" t="n">
+        <v>30</v>
+      </c>
+      <c r="J27" t="n">
+        <v>30</v>
+      </c>
+      <c r="K27" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -690,7 +1437,34 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>245.82</v>
+        <v>176.93</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1547.95</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1638.61</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2042.44</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2362.63</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1947.56</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1702.68</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1570.08</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2032.85</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2434.39</v>
       </c>
     </row>
   </sheetData>
